--- a/procedure_lookup_project.xlsx
+++ b/procedure_lookup_project.xlsx
@@ -13874,24 +13874,24 @@
     </row>
     <row r="524">
       <c r="A524" s="1">
-        <v>615.0</v>
+        <v>616.0</v>
       </c>
       <c r="B524" s="1">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="C524" s="1">
         <v>9.0</v>
       </c>
       <c r="D524" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="1">
-        <v>616.0</v>
+        <v>617.0</v>
       </c>
       <c r="B525" s="1">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="C525" s="1">
         <v>9.0</v>
@@ -13902,7 +13902,7 @@
     </row>
     <row r="526">
       <c r="A526" s="1">
-        <v>617.0</v>
+        <v>618.0</v>
       </c>
       <c r="B526" s="1">
         <v>32.0</v>
@@ -13911,29 +13911,29 @@
         <v>9.0</v>
       </c>
       <c r="D526" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="1">
-        <v>618.0</v>
+        <v>619.0</v>
       </c>
       <c r="B527" s="1">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="C527" s="1">
         <v>9.0</v>
       </c>
       <c r="D527" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="1">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="B528" s="1">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="C528" s="1">
         <v>9.0</v>
@@ -13944,10 +13944,10 @@
     </row>
     <row r="529">
       <c r="A529" s="1">
-        <v>620.0</v>
+        <v>621.0</v>
       </c>
       <c r="B529" s="1">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="C529" s="1">
         <v>9.0</v>
@@ -13958,10 +13958,10 @@
     </row>
     <row r="530">
       <c r="A530" s="1">
-        <v>621.0</v>
+        <v>622.0</v>
       </c>
       <c r="B530" s="1">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="C530" s="1">
         <v>9.0</v>
@@ -13972,10 +13972,10 @@
     </row>
     <row r="531">
       <c r="A531" s="1">
-        <v>622.0</v>
+        <v>623.0</v>
       </c>
       <c r="B531" s="1">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="C531" s="1">
         <v>9.0</v>
@@ -13986,10 +13986,10 @@
     </row>
     <row r="532">
       <c r="A532" s="1">
-        <v>623.0</v>
+        <v>624.0</v>
       </c>
       <c r="B532" s="1">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="C532" s="1">
         <v>9.0</v>
@@ -14000,10 +14000,10 @@
     </row>
     <row r="533">
       <c r="A533" s="1">
-        <v>624.0</v>
+        <v>625.0</v>
       </c>
       <c r="B533" s="1">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="C533" s="1">
         <v>9.0</v>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="534">
       <c r="A534" s="1">
-        <v>625.0</v>
+        <v>626.0</v>
       </c>
       <c r="B534" s="1">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="C534" s="1">
         <v>9.0</v>
@@ -14028,10 +14028,10 @@
     </row>
     <row r="535">
       <c r="A535" s="1">
-        <v>626.0</v>
+        <v>627.0</v>
       </c>
       <c r="B535" s="1">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="C535" s="1">
         <v>9.0</v>
@@ -14039,13 +14039,16 @@
       <c r="D535" s="1">
         <v>1.0</v>
       </c>
+      <c r="E535" s="1" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="1">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="B536" s="1">
-        <v>42.0</v>
+        <v>57.0</v>
       </c>
       <c r="C536" s="1">
         <v>9.0</v>
@@ -14054,15 +14057,15 @@
         <v>1.0</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="1">
-        <v>628.0</v>
+        <v>629.0</v>
       </c>
       <c r="B537" s="1">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="C537" s="1">
         <v>9.0</v>
@@ -14076,10 +14079,10 @@
     </row>
     <row r="538">
       <c r="A538" s="1">
-        <v>629.0</v>
+        <v>630.0</v>
       </c>
       <c r="B538" s="1">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="C538" s="1">
         <v>9.0</v>
@@ -14093,10 +14096,10 @@
     </row>
     <row r="539">
       <c r="A539" s="1">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="B539" s="1">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="C539" s="1">
         <v>9.0</v>
@@ -14110,10 +14113,10 @@
     </row>
     <row r="540">
       <c r="A540" s="1">
-        <v>631.0</v>
+        <v>632.0</v>
       </c>
       <c r="B540" s="1">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="C540" s="1">
         <v>9.0</v>
@@ -14122,15 +14125,15 @@
         <v>1.0</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="1">
-        <v>632.0</v>
+        <v>633.0</v>
       </c>
       <c r="B541" s="1">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="C541" s="1">
         <v>9.0</v>
@@ -14139,21 +14142,21 @@
         <v>1.0</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="1">
-        <v>633.0</v>
+        <v>634.0</v>
       </c>
       <c r="B542" s="1">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="C542" s="1">
         <v>9.0</v>
       </c>
       <c r="D542" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>424</v>
@@ -14161,10 +14164,10 @@
     </row>
     <row r="543">
       <c r="A543" s="1">
-        <v>634.0</v>
+        <v>635.0</v>
       </c>
       <c r="B543" s="1">
-        <v>65.0</v>
+        <v>111.0</v>
       </c>
       <c r="C543" s="1">
         <v>9.0</v>
@@ -14172,36 +14175,36 @@
       <c r="D543" s="1">
         <v>2.0</v>
       </c>
-      <c r="E543" s="1" t="s">
-        <v>424</v>
-      </c>
     </row>
     <row r="544">
       <c r="A544" s="1">
-        <v>635.0</v>
+        <v>636.0</v>
       </c>
       <c r="B544" s="1">
-        <v>111.0</v>
+        <v>66.0</v>
       </c>
       <c r="C544" s="1">
         <v>9.0</v>
       </c>
       <c r="D544" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="E544" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="1">
-        <v>636.0</v>
+        <v>637.0</v>
       </c>
       <c r="B545" s="1">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="C545" s="1">
         <v>9.0</v>
       </c>
       <c r="D545" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>427</v>
@@ -14209,10 +14212,10 @@
     </row>
     <row r="546">
       <c r="A546" s="1">
-        <v>637.0</v>
+        <v>638.0</v>
       </c>
       <c r="B546" s="1">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
       <c r="C546" s="1">
         <v>9.0</v>
@@ -14221,15 +14224,15 @@
         <v>2.0</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="1">
-        <v>638.0</v>
+        <v>639.0</v>
       </c>
       <c r="B547" s="1">
-        <v>70.0</v>
+        <v>77.0</v>
       </c>
       <c r="C547" s="1">
         <v>9.0</v>
@@ -14243,10 +14246,10 @@
     </row>
     <row r="548">
       <c r="A548" s="1">
-        <v>639.0</v>
+        <v>640.0</v>
       </c>
       <c r="B548" s="1">
-        <v>77.0</v>
+        <v>82.0</v>
       </c>
       <c r="C548" s="1">
         <v>9.0</v>
@@ -14260,27 +14263,24 @@
     </row>
     <row r="549">
       <c r="A549" s="1">
-        <v>640.0</v>
+        <v>641.0</v>
       </c>
       <c r="B549" s="1">
-        <v>82.0</v>
+        <v>1.0</v>
       </c>
       <c r="C549" s="1">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D549" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="E549" s="1" t="s">
-        <v>428</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="1">
-        <v>641.0</v>
+        <v>642.0</v>
       </c>
       <c r="B550" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C550" s="1">
         <v>11.0</v>
@@ -14291,10 +14291,10 @@
     </row>
     <row r="551">
       <c r="A551" s="1">
-        <v>642.0</v>
+        <v>643.0</v>
       </c>
       <c r="B551" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C551" s="1">
         <v>11.0</v>
@@ -14305,10 +14305,10 @@
     </row>
     <row r="552">
       <c r="A552" s="1">
-        <v>643.0</v>
+        <v>644.0</v>
       </c>
       <c r="B552" s="1">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C552" s="1">
         <v>11.0</v>
@@ -14319,10 +14319,10 @@
     </row>
     <row r="553">
       <c r="A553" s="1">
-        <v>644.0</v>
+        <v>645.0</v>
       </c>
       <c r="B553" s="1">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C553" s="1">
         <v>11.0</v>
@@ -14333,10 +14333,10 @@
     </row>
     <row r="554">
       <c r="A554" s="1">
-        <v>645.0</v>
+        <v>646.0</v>
       </c>
       <c r="B554" s="1">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="C554" s="1">
         <v>11.0</v>
@@ -14347,10 +14347,10 @@
     </row>
     <row r="555">
       <c r="A555" s="1">
-        <v>646.0</v>
+        <v>647.0</v>
       </c>
       <c r="B555" s="1">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="C555" s="1">
         <v>11.0</v>
@@ -14361,10 +14361,10 @@
     </row>
     <row r="556">
       <c r="A556" s="1">
-        <v>647.0</v>
+        <v>648.0</v>
       </c>
       <c r="B556" s="1">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="C556" s="1">
         <v>11.0</v>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="557">
       <c r="A557" s="1">
-        <v>648.0</v>
+        <v>649.0</v>
       </c>
       <c r="B557" s="1">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="C557" s="1">
         <v>11.0</v>
@@ -14389,10 +14389,10 @@
     </row>
     <row r="558">
       <c r="A558" s="1">
-        <v>649.0</v>
+        <v>650.0</v>
       </c>
       <c r="B558" s="1">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C558" s="1">
         <v>11.0</v>
@@ -14403,10 +14403,10 @@
     </row>
     <row r="559">
       <c r="A559" s="1">
-        <v>650.0</v>
+        <v>651.0</v>
       </c>
       <c r="B559" s="1">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C559" s="1">
         <v>11.0</v>
@@ -14417,10 +14417,10 @@
     </row>
     <row r="560">
       <c r="A560" s="1">
-        <v>651.0</v>
+        <v>652.0</v>
       </c>
       <c r="B560" s="1">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="C560" s="1">
         <v>11.0</v>
@@ -14431,10 +14431,10 @@
     </row>
     <row r="561">
       <c r="A561" s="1">
-        <v>652.0</v>
+        <v>653.0</v>
       </c>
       <c r="B561" s="1">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C561" s="1">
         <v>11.0</v>
@@ -14445,10 +14445,10 @@
     </row>
     <row r="562">
       <c r="A562" s="1">
-        <v>653.0</v>
+        <v>654.0</v>
       </c>
       <c r="B562" s="1">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="C562" s="1">
         <v>11.0</v>
@@ -14459,10 +14459,10 @@
     </row>
     <row r="563">
       <c r="A563" s="1">
-        <v>654.0</v>
+        <v>655.0</v>
       </c>
       <c r="B563" s="1">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="C563" s="1">
         <v>11.0</v>
@@ -14473,10 +14473,10 @@
     </row>
     <row r="564">
       <c r="A564" s="1">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="B564" s="1">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C564" s="1">
         <v>11.0</v>
@@ -14487,10 +14487,10 @@
     </row>
     <row r="565">
       <c r="A565" s="1">
-        <v>656.0</v>
+        <v>657.0</v>
       </c>
       <c r="B565" s="1">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C565" s="1">
         <v>11.0</v>
@@ -14501,10 +14501,10 @@
     </row>
     <row r="566">
       <c r="A566" s="1">
-        <v>657.0</v>
+        <v>658.0</v>
       </c>
       <c r="B566" s="1">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C566" s="1">
         <v>11.0</v>
@@ -14515,10 +14515,10 @@
     </row>
     <row r="567">
       <c r="A567" s="1">
-        <v>658.0</v>
+        <v>659.0</v>
       </c>
       <c r="B567" s="1">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C567" s="1">
         <v>11.0</v>
@@ -14529,10 +14529,10 @@
     </row>
     <row r="568">
       <c r="A568" s="1">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="B568" s="1">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C568" s="1">
         <v>11.0</v>
@@ -14543,10 +14543,10 @@
     </row>
     <row r="569">
       <c r="A569" s="1">
-        <v>660.0</v>
+        <v>661.0</v>
       </c>
       <c r="B569" s="1">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C569" s="1">
         <v>11.0</v>
@@ -14557,10 +14557,10 @@
     </row>
     <row r="570">
       <c r="A570" s="1">
-        <v>661.0</v>
+        <v>662.0</v>
       </c>
       <c r="B570" s="1">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C570" s="1">
         <v>11.0</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="571">
       <c r="A571" s="1">
-        <v>662.0</v>
+        <v>663.0</v>
       </c>
       <c r="B571" s="1">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C571" s="1">
         <v>11.0</v>
@@ -14585,10 +14585,10 @@
     </row>
     <row r="572">
       <c r="A572" s="1">
-        <v>663.0</v>
+        <v>664.0</v>
       </c>
       <c r="B572" s="1">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C572" s="1">
         <v>11.0</v>
@@ -14599,10 +14599,10 @@
     </row>
     <row r="573">
       <c r="A573" s="1">
-        <v>664.0</v>
+        <v>665.0</v>
       </c>
       <c r="B573" s="1">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="C573" s="1">
         <v>11.0</v>
@@ -14613,10 +14613,10 @@
     </row>
     <row r="574">
       <c r="A574" s="1">
-        <v>665.0</v>
+        <v>666.0</v>
       </c>
       <c r="B574" s="1">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="C574" s="1">
         <v>11.0</v>
@@ -14627,10 +14627,10 @@
     </row>
     <row r="575">
       <c r="A575" s="1">
-        <v>666.0</v>
+        <v>667.0</v>
       </c>
       <c r="B575" s="1">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="C575" s="1">
         <v>11.0</v>
@@ -14641,10 +14641,10 @@
     </row>
     <row r="576">
       <c r="A576" s="1">
-        <v>667.0</v>
+        <v>668.0</v>
       </c>
       <c r="B576" s="1">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="C576" s="1">
         <v>11.0</v>
@@ -14655,10 +14655,10 @@
     </row>
     <row r="577">
       <c r="A577" s="1">
-        <v>668.0</v>
+        <v>669.0</v>
       </c>
       <c r="B577" s="1">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="C577" s="1">
         <v>11.0</v>
@@ -14669,10 +14669,10 @@
     </row>
     <row r="578">
       <c r="A578" s="1">
-        <v>669.0</v>
+        <v>670.0</v>
       </c>
       <c r="B578" s="1">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="C578" s="1">
         <v>11.0</v>
@@ -14683,10 +14683,10 @@
     </row>
     <row r="579">
       <c r="A579" s="1">
-        <v>670.0</v>
+        <v>671.0</v>
       </c>
       <c r="B579" s="1">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="C579" s="1">
         <v>11.0</v>
@@ -14697,10 +14697,10 @@
     </row>
     <row r="580">
       <c r="A580" s="1">
-        <v>671.0</v>
+        <v>672.0</v>
       </c>
       <c r="B580" s="1">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="C580" s="1">
         <v>11.0</v>
@@ -14711,10 +14711,10 @@
     </row>
     <row r="581">
       <c r="A581" s="1">
-        <v>672.0</v>
+        <v>673.0</v>
       </c>
       <c r="B581" s="1">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="C581" s="1">
         <v>11.0</v>
@@ -14725,10 +14725,10 @@
     </row>
     <row r="582">
       <c r="A582" s="1">
-        <v>673.0</v>
+        <v>674.0</v>
       </c>
       <c r="B582" s="1">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="C582" s="1">
         <v>11.0</v>
@@ -14739,10 +14739,10 @@
     </row>
     <row r="583">
       <c r="A583" s="1">
-        <v>674.0</v>
+        <v>675.0</v>
       </c>
       <c r="B583" s="1">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="C583" s="1">
         <v>11.0</v>
@@ -14753,10 +14753,10 @@
     </row>
     <row r="584">
       <c r="A584" s="1">
-        <v>675.0</v>
+        <v>676.0</v>
       </c>
       <c r="B584" s="1">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="C584" s="1">
         <v>11.0</v>
@@ -14767,10 +14767,10 @@
     </row>
     <row r="585">
       <c r="A585" s="1">
-        <v>676.0</v>
+        <v>677.0</v>
       </c>
       <c r="B585" s="1">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="C585" s="1">
         <v>11.0</v>
@@ -14781,10 +14781,10 @@
     </row>
     <row r="586">
       <c r="A586" s="1">
-        <v>677.0</v>
+        <v>678.0</v>
       </c>
       <c r="B586" s="1">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="C586" s="1">
         <v>11.0</v>
@@ -14795,10 +14795,10 @@
     </row>
     <row r="587">
       <c r="A587" s="1">
-        <v>678.0</v>
+        <v>679.0</v>
       </c>
       <c r="B587" s="1">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="C587" s="1">
         <v>11.0</v>
@@ -14809,10 +14809,10 @@
     </row>
     <row r="588">
       <c r="A588" s="1">
-        <v>679.0</v>
+        <v>680.0</v>
       </c>
       <c r="B588" s="1">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="C588" s="1">
         <v>11.0</v>
@@ -14820,30 +14820,33 @@
       <c r="D588" s="1">
         <v>1.0</v>
       </c>
+      <c r="E588" s="1" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="1">
-        <v>680.0</v>
+        <v>681.0</v>
       </c>
       <c r="B589" s="1">
-        <v>42.0</v>
+        <v>63.0</v>
       </c>
       <c r="C589" s="1">
         <v>11.0</v>
       </c>
       <c r="D589" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="1">
-        <v>681.0</v>
+        <v>682.0</v>
       </c>
       <c r="B590" s="1">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="C590" s="1">
         <v>11.0</v>
@@ -14851,16 +14854,13 @@
       <c r="D590" s="1">
         <v>2.0</v>
       </c>
-      <c r="E590" s="1" t="s">
-        <v>426</v>
-      </c>
     </row>
     <row r="591">
       <c r="A591" s="1">
-        <v>682.0</v>
+        <v>683.0</v>
       </c>
       <c r="B591" s="1">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="C591" s="1">
         <v>11.0</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="592">
       <c r="A592" s="1">
-        <v>683.0</v>
+        <v>684.0</v>
       </c>
       <c r="B592" s="1">
-        <v>65.0</v>
+        <v>111.0</v>
       </c>
       <c r="C592" s="1">
         <v>11.0</v>
@@ -14885,10 +14885,10 @@
     </row>
     <row r="593">
       <c r="A593" s="1">
-        <v>684.0</v>
+        <v>685.0</v>
       </c>
       <c r="B593" s="1">
-        <v>111.0</v>
+        <v>66.0</v>
       </c>
       <c r="C593" s="1">
         <v>11.0</v>
@@ -14896,13 +14896,16 @@
       <c r="D593" s="1">
         <v>2.0</v>
       </c>
+      <c r="E593" s="1" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="1">
-        <v>685.0</v>
+        <v>686.0</v>
       </c>
       <c r="B594" s="1">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="C594" s="1">
         <v>11.0</v>
@@ -14910,30 +14913,27 @@
       <c r="D594" s="1">
         <v>2.0</v>
       </c>
-      <c r="E594" s="1" t="s">
-        <v>427</v>
-      </c>
     </row>
     <row r="595">
       <c r="A595" s="1">
-        <v>686.0</v>
+        <v>687.0</v>
       </c>
       <c r="B595" s="1">
-        <v>67.0</v>
+        <v>1.0</v>
       </c>
       <c r="C595" s="1">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D595" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="1">
-        <v>687.0</v>
+        <v>688.0</v>
       </c>
       <c r="B596" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C596" s="1">
         <v>12.0</v>
@@ -14944,10 +14944,10 @@
     </row>
     <row r="597">
       <c r="A597" s="1">
-        <v>688.0</v>
+        <v>689.0</v>
       </c>
       <c r="B597" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C597" s="1">
         <v>12.0</v>
@@ -14958,10 +14958,10 @@
     </row>
     <row r="598">
       <c r="A598" s="1">
-        <v>689.0</v>
+        <v>690.0</v>
       </c>
       <c r="B598" s="1">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C598" s="1">
         <v>12.0</v>
@@ -14972,10 +14972,10 @@
     </row>
     <row r="599">
       <c r="A599" s="1">
-        <v>690.0</v>
+        <v>691.0</v>
       </c>
       <c r="B599" s="1">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C599" s="1">
         <v>12.0</v>
@@ -14986,10 +14986,10 @@
     </row>
     <row r="600">
       <c r="A600" s="1">
-        <v>691.0</v>
+        <v>692.0</v>
       </c>
       <c r="B600" s="1">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="C600" s="1">
         <v>12.0</v>
@@ -15000,10 +15000,10 @@
     </row>
     <row r="601">
       <c r="A601" s="1">
-        <v>692.0</v>
+        <v>693.0</v>
       </c>
       <c r="B601" s="1">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="C601" s="1">
         <v>12.0</v>
@@ -15014,10 +15014,10 @@
     </row>
     <row r="602">
       <c r="A602" s="1">
-        <v>693.0</v>
+        <v>694.0</v>
       </c>
       <c r="B602" s="1">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="C602" s="1">
         <v>12.0</v>
@@ -15028,10 +15028,10 @@
     </row>
     <row r="603">
       <c r="A603" s="1">
-        <v>694.0</v>
+        <v>695.0</v>
       </c>
       <c r="B603" s="1">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="C603" s="1">
         <v>12.0</v>
@@ -15042,10 +15042,10 @@
     </row>
     <row r="604">
       <c r="A604" s="1">
-        <v>695.0</v>
+        <v>696.0</v>
       </c>
       <c r="B604" s="1">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C604" s="1">
         <v>12.0</v>
@@ -15056,10 +15056,10 @@
     </row>
     <row r="605">
       <c r="A605" s="1">
-        <v>696.0</v>
+        <v>697.0</v>
       </c>
       <c r="B605" s="1">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C605" s="1">
         <v>12.0</v>
@@ -15070,10 +15070,10 @@
     </row>
     <row r="606">
       <c r="A606" s="1">
-        <v>697.0</v>
+        <v>698.0</v>
       </c>
       <c r="B606" s="1">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="C606" s="1">
         <v>12.0</v>
@@ -15084,10 +15084,10 @@
     </row>
     <row r="607">
       <c r="A607" s="1">
-        <v>698.0</v>
+        <v>699.0</v>
       </c>
       <c r="B607" s="1">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C607" s="1">
         <v>12.0</v>
@@ -15098,10 +15098,10 @@
     </row>
     <row r="608">
       <c r="A608" s="1">
-        <v>699.0</v>
+        <v>700.0</v>
       </c>
       <c r="B608" s="1">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="C608" s="1">
         <v>12.0</v>
@@ -15112,10 +15112,10 @@
     </row>
     <row r="609">
       <c r="A609" s="1">
-        <v>700.0</v>
+        <v>701.0</v>
       </c>
       <c r="B609" s="1">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="C609" s="1">
         <v>12.0</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="610">
       <c r="A610" s="1">
-        <v>701.0</v>
+        <v>702.0</v>
       </c>
       <c r="B610" s="1">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C610" s="1">
         <v>12.0</v>
@@ -15140,10 +15140,10 @@
     </row>
     <row r="611">
       <c r="A611" s="1">
-        <v>702.0</v>
+        <v>703.0</v>
       </c>
       <c r="B611" s="1">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C611" s="1">
         <v>12.0</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="612">
       <c r="A612" s="1">
-        <v>703.0</v>
+        <v>704.0</v>
       </c>
       <c r="B612" s="1">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C612" s="1">
         <v>12.0</v>
@@ -15168,10 +15168,10 @@
     </row>
     <row r="613">
       <c r="A613" s="1">
-        <v>704.0</v>
+        <v>705.0</v>
       </c>
       <c r="B613" s="1">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C613" s="1">
         <v>12.0</v>
@@ -15182,10 +15182,10 @@
     </row>
     <row r="614">
       <c r="A614" s="1">
-        <v>705.0</v>
+        <v>706.0</v>
       </c>
       <c r="B614" s="1">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C614" s="1">
         <v>12.0</v>
@@ -15196,10 +15196,10 @@
     </row>
     <row r="615">
       <c r="A615" s="1">
-        <v>706.0</v>
+        <v>707.0</v>
       </c>
       <c r="B615" s="1">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C615" s="1">
         <v>12.0</v>
@@ -15210,10 +15210,10 @@
     </row>
     <row r="616">
       <c r="A616" s="1">
-        <v>707.0</v>
+        <v>708.0</v>
       </c>
       <c r="B616" s="1">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C616" s="1">
         <v>12.0</v>
@@ -15224,10 +15224,10 @@
     </row>
     <row r="617">
       <c r="A617" s="1">
-        <v>708.0</v>
+        <v>709.0</v>
       </c>
       <c r="B617" s="1">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C617" s="1">
         <v>12.0</v>
@@ -15238,10 +15238,10 @@
     </row>
     <row r="618">
       <c r="A618" s="1">
-        <v>709.0</v>
+        <v>710.0</v>
       </c>
       <c r="B618" s="1">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C618" s="1">
         <v>12.0</v>
@@ -15252,10 +15252,10 @@
     </row>
     <row r="619">
       <c r="A619" s="1">
-        <v>710.0</v>
+        <v>711.0</v>
       </c>
       <c r="B619" s="1">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="C619" s="1">
         <v>12.0</v>
@@ -15266,10 +15266,10 @@
     </row>
     <row r="620">
       <c r="A620" s="1">
-        <v>711.0</v>
+        <v>712.0</v>
       </c>
       <c r="B620" s="1">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="C620" s="1">
         <v>12.0</v>
@@ -15280,10 +15280,10 @@
     </row>
     <row r="621">
       <c r="A621" s="1">
-        <v>712.0</v>
+        <v>713.0</v>
       </c>
       <c r="B621" s="1">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="C621" s="1">
         <v>12.0</v>
@@ -15294,10 +15294,10 @@
     </row>
     <row r="622">
       <c r="A622" s="1">
-        <v>713.0</v>
+        <v>714.0</v>
       </c>
       <c r="B622" s="1">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="C622" s="1">
         <v>12.0</v>
@@ -15308,10 +15308,10 @@
     </row>
     <row r="623">
       <c r="A623" s="1">
-        <v>714.0</v>
+        <v>715.0</v>
       </c>
       <c r="B623" s="1">
-        <v>28.0</v>
+        <v>110.0</v>
       </c>
       <c r="C623" s="1">
         <v>12.0</v>
@@ -15322,10 +15322,10 @@
     </row>
     <row r="624">
       <c r="A624" s="1">
-        <v>715.0</v>
+        <v>716.0</v>
       </c>
       <c r="B624" s="1">
-        <v>110.0</v>
+        <v>29.0</v>
       </c>
       <c r="C624" s="1">
         <v>12.0</v>
@@ -15336,10 +15336,10 @@
     </row>
     <row r="625">
       <c r="A625" s="1">
-        <v>716.0</v>
+        <v>717.0</v>
       </c>
       <c r="B625" s="1">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="C625" s="1">
         <v>12.0</v>
@@ -15350,10 +15350,10 @@
     </row>
     <row r="626">
       <c r="A626" s="1">
-        <v>717.0</v>
+        <v>718.0</v>
       </c>
       <c r="B626" s="1">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="C626" s="1">
         <v>12.0</v>
@@ -15364,10 +15364,10 @@
     </row>
     <row r="627">
       <c r="A627" s="1">
-        <v>718.0</v>
+        <v>719.0</v>
       </c>
       <c r="B627" s="1">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="C627" s="1">
         <v>12.0</v>
@@ -15378,10 +15378,10 @@
     </row>
     <row r="628">
       <c r="A628" s="1">
-        <v>719.0</v>
+        <v>720.0</v>
       </c>
       <c r="B628" s="1">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="C628" s="1">
         <v>12.0</v>
@@ -15392,10 +15392,10 @@
     </row>
     <row r="629">
       <c r="A629" s="1">
-        <v>720.0</v>
+        <v>721.0</v>
       </c>
       <c r="B629" s="1">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="C629" s="1">
         <v>12.0</v>
@@ -15406,10 +15406,10 @@
     </row>
     <row r="630">
       <c r="A630" s="1">
-        <v>721.0</v>
+        <v>722.0</v>
       </c>
       <c r="B630" s="1">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="C630" s="1">
         <v>12.0</v>
@@ -15420,10 +15420,10 @@
     </row>
     <row r="631">
       <c r="A631" s="1">
-        <v>722.0</v>
+        <v>723.0</v>
       </c>
       <c r="B631" s="1">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="C631" s="1">
         <v>12.0</v>
@@ -15434,10 +15434,10 @@
     </row>
     <row r="632">
       <c r="A632" s="1">
-        <v>723.0</v>
+        <v>724.0</v>
       </c>
       <c r="B632" s="1">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="C632" s="1">
         <v>12.0</v>
@@ -15448,10 +15448,10 @@
     </row>
     <row r="633">
       <c r="A633" s="1">
-        <v>724.0</v>
+        <v>725.0</v>
       </c>
       <c r="B633" s="1">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="C633" s="1">
         <v>12.0</v>
@@ -15462,10 +15462,10 @@
     </row>
     <row r="634">
       <c r="A634" s="1">
-        <v>725.0</v>
+        <v>726.0</v>
       </c>
       <c r="B634" s="1">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="C634" s="1">
         <v>12.0</v>
@@ -15476,10 +15476,10 @@
     </row>
     <row r="635">
       <c r="A635" s="1">
-        <v>726.0</v>
+        <v>727.0</v>
       </c>
       <c r="B635" s="1">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="C635" s="1">
         <v>12.0</v>
@@ -15487,13 +15487,16 @@
       <c r="D635" s="1">
         <v>1.0</v>
       </c>
+      <c r="E635" s="1" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="1">
-        <v>727.0</v>
+        <v>728.0</v>
       </c>
       <c r="B636" s="1">
-        <v>42.0</v>
+        <v>63.0</v>
       </c>
       <c r="C636" s="1">
         <v>12.0</v>
@@ -15502,15 +15505,15 @@
         <v>1.0</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="1">
-        <v>728.0</v>
+        <v>729.0</v>
       </c>
       <c r="B637" s="1">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="C637" s="1">
         <v>12.0</v>
@@ -15518,16 +15521,13 @@
       <c r="D637" s="1">
         <v>1.0</v>
       </c>
-      <c r="E637" s="1" t="s">
-        <v>426</v>
-      </c>
     </row>
     <row r="638">
       <c r="A638" s="1">
-        <v>729.0</v>
+        <v>730.0</v>
       </c>
       <c r="B638" s="1">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
       <c r="C638" s="1">
         <v>12.0</v>
@@ -15535,19 +15535,22 @@
       <c r="D638" s="1">
         <v>1.0</v>
       </c>
+      <c r="E638" s="1" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="1">
-        <v>730.0</v>
+        <v>731.0</v>
       </c>
       <c r="B639" s="1">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="C639" s="1">
         <v>12.0</v>
       </c>
       <c r="D639" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E639" s="1" t="s">
         <v>427</v>
@@ -15555,10 +15558,10 @@
     </row>
     <row r="640">
       <c r="A640" s="1">
-        <v>731.0</v>
+        <v>732.0</v>
       </c>
       <c r="B640" s="1">
-        <v>67.0</v>
+        <v>74.0</v>
       </c>
       <c r="C640" s="1">
         <v>12.0</v>
@@ -15567,15 +15570,15 @@
         <v>2.0</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="1">
-        <v>732.0</v>
+        <v>733.0</v>
       </c>
       <c r="B641" s="1">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="C641" s="1">
         <v>12.0</v>
@@ -15589,10 +15592,10 @@
     </row>
     <row r="642">
       <c r="A642" s="1">
-        <v>733.0</v>
+        <v>734.0</v>
       </c>
       <c r="B642" s="1">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="C642" s="1">
         <v>12.0</v>
@@ -15606,10 +15609,10 @@
     </row>
     <row r="643">
       <c r="A643" s="1">
-        <v>734.0</v>
+        <v>735.0</v>
       </c>
       <c r="B643" s="1">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="C643" s="1">
         <v>12.0</v>
@@ -15622,21 +15625,8 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="1">
-        <v>735.0</v>
-      </c>
-      <c r="B644" s="1">
-        <v>80.0</v>
-      </c>
-      <c r="C644" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D644" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="E644" s="1" t="s">
-        <v>428</v>
-      </c>
+      <c r="B644" s="1"/>
+      <c r="D644" s="1"/>
     </row>
     <row r="645">
       <c r="B645" s="1"/>
@@ -19589,10 +19579,6 @@
     <row r="1632">
       <c r="B1632" s="1"/>
       <c r="D1632" s="1"/>
-    </row>
-    <row r="1633">
-      <c r="B1633" s="1"/>
-      <c r="D1633" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/procedure_lookup_project.xlsx
+++ b/procedure_lookup_project.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4210" uniqueCount="712">
   <si>
     <t>RadiologistID</t>
   </si>
@@ -1414,6 +1414,750 @@
   <si>
     <t>AliasType</t>
   </si>
+  <si>
+    <t>Hip Injection</t>
+  </si>
+  <si>
+    <t>Common Name</t>
+  </si>
+  <si>
+    <t>Hip Joint Inj</t>
+  </si>
+  <si>
+    <t>Abbreviation</t>
+  </si>
+  <si>
+    <t>Hip Cortisone</t>
+  </si>
+  <si>
+    <t>Layman Term</t>
+  </si>
+  <si>
+    <t>Hip Shot</t>
+  </si>
+  <si>
+    <t>Medical Term</t>
+  </si>
+  <si>
+    <t>Source Label</t>
+  </si>
+  <si>
+    <t>Hip Aspiration</t>
+  </si>
+  <si>
+    <t>Hip Drain</t>
+  </si>
+  <si>
+    <t>Hip Fluid Removal</t>
+  </si>
+  <si>
+    <t>Aspirate Hip</t>
+  </si>
+  <si>
+    <t>Troch Bursa Injection</t>
+  </si>
+  <si>
+    <t>Greater Troch Injection</t>
+  </si>
+  <si>
+    <t>Hip Bursa Injection</t>
+  </si>
+  <si>
+    <t>Knee Injection</t>
+  </si>
+  <si>
+    <t>Knee Shot</t>
+  </si>
+  <si>
+    <t>Knee Cortisone</t>
+  </si>
+  <si>
+    <t>Knee Aspiration</t>
+  </si>
+  <si>
+    <t>Knee Drain</t>
+  </si>
+  <si>
+    <t>Knee Fluid Removal</t>
+  </si>
+  <si>
+    <t>Ankle Joint Injection</t>
+  </si>
+  <si>
+    <t>Ankle Shot</t>
+  </si>
+  <si>
+    <t>Plantar Fasciitis Injection</t>
+  </si>
+  <si>
+    <t>Heel Injection</t>
+  </si>
+  <si>
+    <t>Foot Cortisone</t>
+  </si>
+  <si>
+    <t>MTP Joint Injection</t>
+  </si>
+  <si>
+    <t>Toe Joint Injection</t>
+  </si>
+  <si>
+    <t>Forefoot Injection</t>
+  </si>
+  <si>
+    <t>Shoulder Injection</t>
+  </si>
+  <si>
+    <t>Shoulder Shot</t>
+  </si>
+  <si>
+    <t>Shoulder Cortisone</t>
+  </si>
+  <si>
+    <t>Sub AC or GH</t>
+  </si>
+  <si>
+    <t>Subacromial Bursa Injection</t>
+  </si>
+  <si>
+    <t>Sub AC Injection</t>
+  </si>
+  <si>
+    <t>Shoulder Bursa Injection</t>
+  </si>
+  <si>
+    <t>Subacromial Injection</t>
+  </si>
+  <si>
+    <t>GH Injection</t>
+  </si>
+  <si>
+    <t>Glenohumeral Injection</t>
+  </si>
+  <si>
+    <t>Shoulder Joint Injection</t>
+  </si>
+  <si>
+    <t>Shoulder GH Injection</t>
+  </si>
+  <si>
+    <t>Booking Term</t>
+  </si>
+  <si>
+    <t>AC Injection</t>
+  </si>
+  <si>
+    <t>Acromioclavicular Injection</t>
+  </si>
+  <si>
+    <t>Shoulder AC Joint Injection</t>
+  </si>
+  <si>
+    <t>Elbow Injection</t>
+  </si>
+  <si>
+    <t>Elbow Shot</t>
+  </si>
+  <si>
+    <t>Golfers Elbow Injection</t>
+  </si>
+  <si>
+    <t>Medial Elbow Injection</t>
+  </si>
+  <si>
+    <t>Tennis Elbow Injection</t>
+  </si>
+  <si>
+    <t>Lateral Elbow Injection</t>
+  </si>
+  <si>
+    <t>1st CMC Injection</t>
+  </si>
+  <si>
+    <t>Thumb CMC Injection</t>
+  </si>
+  <si>
+    <t>Thumb Joint Injection</t>
+  </si>
+  <si>
+    <t>Finger Trigger Injection</t>
+  </si>
+  <si>
+    <t>Trigger Thumb Injection</t>
+  </si>
+  <si>
+    <t>Facet Injection</t>
+  </si>
+  <si>
+    <t>Low Back Facet Injection</t>
+  </si>
+  <si>
+    <t>SI Injection</t>
+  </si>
+  <si>
+    <t>Sacroiliac Injection</t>
+  </si>
+  <si>
+    <t>SI Shot</t>
+  </si>
+  <si>
+    <t>Sit Bone Injection</t>
+  </si>
+  <si>
+    <t>Buttock Bursa Injection</t>
+  </si>
+  <si>
+    <t>Pubic Injection</t>
+  </si>
+  <si>
+    <t>Pes Anserine Injection</t>
+  </si>
+  <si>
+    <t>Knee Bursa Injection</t>
+  </si>
+  <si>
+    <t>Pes Bursa Injection</t>
+  </si>
+  <si>
+    <t>Subtalar Injection</t>
+  </si>
+  <si>
+    <t>Ankle Subtalar Injection</t>
+  </si>
+  <si>
+    <t>Talonavicular Injection</t>
+  </si>
+  <si>
+    <t>TN Joint Injection</t>
+  </si>
+  <si>
+    <t>Heel Bursa Injection</t>
+  </si>
+  <si>
+    <t>Achilles Bursa Injection</t>
+  </si>
+  <si>
+    <t>Toe Shot</t>
+  </si>
+  <si>
+    <t>Hydrodilatation Shoulder</t>
+  </si>
+  <si>
+    <t>Misspelling</t>
+  </si>
+  <si>
+    <t>Frozen Shoulder Injection</t>
+  </si>
+  <si>
+    <t>Shoulder Distension Injection</t>
+  </si>
+  <si>
+    <t>Biceps Injection</t>
+  </si>
+  <si>
+    <t>Shoulder Biceps Injection</t>
+  </si>
+  <si>
+    <t>Elbow Bursa Injection</t>
+  </si>
+  <si>
+    <t>Elbow Swelling Injection</t>
+  </si>
+  <si>
+    <t>Elbow Bursa Drain</t>
+  </si>
+  <si>
+    <t>Elbow Aspiration</t>
+  </si>
+  <si>
+    <t>Radiocarpal Injection</t>
+  </si>
+  <si>
+    <t>Wrist Injection</t>
+  </si>
+  <si>
+    <t>DeQuervains Injection</t>
+  </si>
+  <si>
+    <t>DeQuervain Injection</t>
+  </si>
+  <si>
+    <t>Thumb Tendon Injection</t>
+  </si>
+  <si>
+    <t>Finger Joint Injection</t>
+  </si>
+  <si>
+    <t>Finger Shot</t>
+  </si>
+  <si>
+    <t>Hip Flexor Bursa Injection</t>
+  </si>
+  <si>
+    <t>Psoas Bursa Injection</t>
+  </si>
+  <si>
+    <t>Foot Sinus Tarsi Injection</t>
+  </si>
+  <si>
+    <t>Ankle Sinus Injection</t>
+  </si>
+  <si>
+    <t>Piriformis Shot</t>
+  </si>
+  <si>
+    <t>Buttock Piriformis Injection</t>
+  </si>
+  <si>
+    <t>Proximal Tib Fib Injection</t>
+  </si>
+  <si>
+    <t>Proximal Tibiofibular Injection</t>
+  </si>
+  <si>
+    <t>Tib Fib Joint Injection</t>
+  </si>
+  <si>
+    <t>SC Joint Injection</t>
+  </si>
+  <si>
+    <t>Sternoclavicular Injection</t>
+  </si>
+  <si>
+    <t>TMJ Injection</t>
+  </si>
+  <si>
+    <t>Jaw Joint Injection</t>
+  </si>
+  <si>
+    <t>Temporomandibular Injection</t>
+  </si>
+  <si>
+    <t>Pars Block</t>
+  </si>
+  <si>
+    <t>Pars Injection</t>
+  </si>
+  <si>
+    <t>Coccyx Injection</t>
+  </si>
+  <si>
+    <t>Tailbone Injection</t>
+  </si>
+  <si>
+    <t>TPI</t>
+  </si>
+  <si>
+    <t>Muscle Trigger Injection</t>
+  </si>
+  <si>
+    <t>GLOC Block</t>
+  </si>
+  <si>
+    <t>Occipital Nerve Block</t>
+  </si>
+  <si>
+    <t>Headache Nerve Block</t>
+  </si>
+  <si>
+    <t>Platelet Rich Plasma Injection</t>
+  </si>
+  <si>
+    <t>PRP Shot</t>
+  </si>
+  <si>
+    <t>Discogram</t>
+  </si>
+  <si>
+    <t>Disc Injection Study</t>
+  </si>
+  <si>
+    <t>Neck Facet Injection</t>
+  </si>
+  <si>
+    <t>C Spine Facet Injection</t>
+  </si>
+  <si>
+    <t>C0 C1 Facet Injection</t>
+  </si>
+  <si>
+    <t>Upper Cervical Facet Injection</t>
+  </si>
+  <si>
+    <t>Cervical C0/C1 Injection</t>
+  </si>
+  <si>
+    <t>C1 C2 Facet Injection</t>
+  </si>
+  <si>
+    <t>Cervical C1/C2 Injection</t>
+  </si>
+  <si>
+    <t>Upper Neck Facet Injection</t>
+  </si>
+  <si>
+    <t>Cervical ESI</t>
+  </si>
+  <si>
+    <t>Neck Epidural</t>
+  </si>
+  <si>
+    <t>Cervical Interlaminar ESI</t>
+  </si>
+  <si>
+    <t>Interlaminar Neck Epidural</t>
+  </si>
+  <si>
+    <t>Cervical Interlaminar Epidural</t>
+  </si>
+  <si>
+    <t>C2 Block</t>
+  </si>
+  <si>
+    <t>Occipital C2 Block</t>
+  </si>
+  <si>
+    <t>Third Occipital Block</t>
+  </si>
+  <si>
+    <t>TON Block</t>
+  </si>
+  <si>
+    <t>SPGB</t>
+  </si>
+  <si>
+    <t>Migraine Ganglion Block</t>
+  </si>
+  <si>
+    <t>Mid Back Facet Injection</t>
+  </si>
+  <si>
+    <t>T Spine Facet Injection</t>
+  </si>
+  <si>
+    <t>Thoracic ESI</t>
+  </si>
+  <si>
+    <t>Thoracic Epidural</t>
+  </si>
+  <si>
+    <t>Intercostal Block</t>
+  </si>
+  <si>
+    <t>Rib Nerve Block</t>
+  </si>
+  <si>
+    <t>Lumbar NRB</t>
+  </si>
+  <si>
+    <t>Nerve Root Block</t>
+  </si>
+  <si>
+    <t>S1 NRB</t>
+  </si>
+  <si>
+    <t>Sciatica Nerve Root Injection</t>
+  </si>
+  <si>
+    <t>Lumbar TFESI</t>
+  </si>
+  <si>
+    <t>Transforaminal ESI</t>
+  </si>
+  <si>
+    <t>Lumbar Transforaminal Epidural</t>
+  </si>
+  <si>
+    <t>Lumbar Interlaminar ESI</t>
+  </si>
+  <si>
+    <t>Low Back Epidural</t>
+  </si>
+  <si>
+    <t>Lumbar Interlaminar Epidural</t>
+  </si>
+  <si>
+    <t>Caudal ESI</t>
+  </si>
+  <si>
+    <t>Caudal Epidural</t>
+  </si>
+  <si>
+    <t>Tailbone Epidural</t>
+  </si>
+  <si>
+    <t>Pudendal Block</t>
+  </si>
+  <si>
+    <t>Pelvic Nerve Block</t>
+  </si>
+  <si>
+    <t>Bakers Cyst Aspiration</t>
+  </si>
+  <si>
+    <t>Baker Cyst Drain</t>
+  </si>
+  <si>
+    <t>Popliteal Cyst Aspiration</t>
+  </si>
+  <si>
+    <t>Wrist Nerve Injection</t>
+  </si>
+  <si>
+    <t>CTS Injection</t>
+  </si>
+  <si>
+    <t>Patellar Bursa Injection</t>
+  </si>
+  <si>
+    <t>Ganglion Cyst Aspiration Hand</t>
+  </si>
+  <si>
+    <t>Wrist Ganglion Drain</t>
+  </si>
+  <si>
+    <t>Ganglion Cyst Aspiration Wrist</t>
+  </si>
+  <si>
+    <t>Ganglion Cyst Aspiration</t>
+  </si>
+  <si>
+    <t>Ganglion Drain</t>
+  </si>
+  <si>
+    <t>Cyst Aspiration</t>
+  </si>
+  <si>
+    <t>Generic Search</t>
+  </si>
+  <si>
+    <t>Gluteal Bursa Injection</t>
+  </si>
+  <si>
+    <t>Hamstring Injection</t>
+  </si>
+  <si>
+    <t>Proximal Hamstring Injection</t>
+  </si>
+  <si>
+    <t>Forefoot Bursa Injection</t>
+  </si>
+  <si>
+    <t>Foot Bursa Injection</t>
+  </si>
+  <si>
+    <t>Ilioinguinal Block</t>
+  </si>
+  <si>
+    <t>Groin Nerve Block</t>
+  </si>
+  <si>
+    <t>IT Band Injection</t>
+  </si>
+  <si>
+    <t>Outer Knee Injection</t>
+  </si>
+  <si>
+    <t>LFCN Block</t>
+  </si>
+  <si>
+    <t>Meralgia Paresthetica Injection</t>
+  </si>
+  <si>
+    <t>Foot Neuroma Injection</t>
+  </si>
+  <si>
+    <t>Mortons Injection</t>
+  </si>
+  <si>
+    <t>Percutaneous Needle Tenotomy</t>
+  </si>
+  <si>
+    <t>Tendon Tenotomy</t>
+  </si>
+  <si>
+    <t>Tendonosis Needling</t>
+  </si>
+  <si>
+    <t>Peroneal Tendon Injection</t>
+  </si>
+  <si>
+    <t>Outer Ankle Tendon Injection</t>
+  </si>
+  <si>
+    <t>Foot Fibroma Injection</t>
+  </si>
+  <si>
+    <t>Arch Fibroma Injection</t>
+  </si>
+  <si>
+    <t>Posterior Tibialis Injection</t>
+  </si>
+  <si>
+    <t>Inner Ankle Tendon Injection</t>
+  </si>
+  <si>
+    <t>Tasral Tunnel Injection</t>
+  </si>
+  <si>
+    <t>Ankle Nerve Injection</t>
+  </si>
+  <si>
+    <t>Achilles PRP</t>
+  </si>
+  <si>
+    <t>PRP Achilles Injection</t>
+  </si>
+  <si>
+    <t>Calcific Tendon Lavage</t>
+  </si>
+  <si>
+    <t>Shoulder Calcification Injection</t>
+  </si>
+  <si>
+    <t>Elbow Nerve Injection</t>
+  </si>
+  <si>
+    <t>Ulnar Nerve Injection</t>
+  </si>
+  <si>
+    <t>ECU Injection</t>
+  </si>
+  <si>
+    <t>Wrist ECU Injection</t>
+  </si>
+  <si>
+    <t>Stellate Block</t>
+  </si>
+  <si>
+    <t>Sympathetic Nerve Block</t>
+  </si>
+  <si>
+    <t>Sciatic Block</t>
+  </si>
+  <si>
+    <t>Sciatica Injection</t>
+  </si>
+  <si>
+    <t>Dupuytrens Injection</t>
+  </si>
+  <si>
+    <t>Hand Contracture Injection</t>
+  </si>
+  <si>
+    <t>Lumbar MBB</t>
+  </si>
+  <si>
+    <t>Medial Branch Block</t>
+  </si>
+  <si>
+    <t>SI MBB</t>
+  </si>
+  <si>
+    <t>Sacroiliac Medial Branch Block</t>
+  </si>
+  <si>
+    <t>Suprascapular Block</t>
+  </si>
+  <si>
+    <t>Shoulder Nerve Block</t>
+  </si>
+  <si>
+    <t>Neck Medial Branch Block</t>
+  </si>
+  <si>
+    <t>Mid Back Medial Branch Block</t>
+  </si>
+  <si>
+    <t>Stereo Biopsy</t>
+  </si>
+  <si>
+    <t>Breast Stereo BX</t>
+  </si>
+  <si>
+    <t>Breast Wire Localization</t>
+  </si>
+  <si>
+    <t>FNA</t>
+  </si>
+  <si>
+    <t>Fine Needle Aspiration</t>
+  </si>
+  <si>
+    <t>Thyroid FNA</t>
+  </si>
+  <si>
+    <t>Common Search</t>
+  </si>
+  <si>
+    <t>Thyroid Needle Biopsy</t>
+  </si>
+  <si>
+    <t>Breast Needle Biopsy</t>
+  </si>
+  <si>
+    <t>MSK Biopsy</t>
+  </si>
+  <si>
+    <t>Salivary Biopsy</t>
+  </si>
+  <si>
+    <t>Groin Needle Biopsy</t>
+  </si>
+  <si>
+    <t>Armpit Biopsy</t>
+  </si>
+  <si>
+    <t>Neck Needle Biopsy</t>
+  </si>
+  <si>
+    <t>Genicular Nerve Block</t>
+  </si>
+  <si>
+    <t>Knee Nerve Block</t>
+  </si>
+  <si>
+    <t>Genicular Block</t>
+  </si>
+  <si>
+    <t>Knee RFA</t>
+  </si>
+  <si>
+    <t>Knee RFN</t>
+  </si>
+  <si>
+    <t>Thoracic RFA</t>
+  </si>
+  <si>
+    <t>Neck Radiofrequency Ablation</t>
+  </si>
+  <si>
+    <t>Low Back RFA</t>
+  </si>
+  <si>
+    <t>SI Joint Radiofrequency</t>
+  </si>
+  <si>
+    <t>Wrist Arthro</t>
+  </si>
+  <si>
+    <t>MR Wrist Arthrogram</t>
+  </si>
+  <si>
+    <t>Shoulder Arthro</t>
+  </si>
+  <si>
+    <t>MR Shoulder Arthrogram</t>
+  </si>
+  <si>
+    <t>Prepatellar Bursa Injection</t>
+  </si>
+  <si>
+    <t>Pre Patellar Bursa Injection</t>
+  </si>
+  <si>
+    <t>Kneecap Bursa Injection</t>
+  </si>
 </sst>
 </file>
 
@@ -2881,6 +3625,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.0"/>
+    <col customWidth="1" min="3" max="3" width="31.63"/>
+    <col customWidth="1" min="4" max="4" width="13.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2895,6 +3641,4878 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>463</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="B23" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="B24" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="B25" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="B26" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="B31" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="B32" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="B33" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="B34" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="B35" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="B36" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="B52" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="B53" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="B54" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="B55" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="B56" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="B57" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="B58" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="B59" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="B60" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="B61" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="B62" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="B63" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="B64" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="B65" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="B66" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="B67" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="B68" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="B69" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="B70" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="B71" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="B72" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="B73" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="B74" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="B75" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="B76" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="B77" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="B78" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="B79" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="B80" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="B81" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="B82" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="B83" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="B84" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="B85" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="B86" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="B87" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="B88" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="B89" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="B90" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="B91" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="B92" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="B93" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="B94" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="B95" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="B96" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="B97" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1">
+        <v>97.0</v>
+      </c>
+      <c r="B98" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1">
+        <v>98.0</v>
+      </c>
+      <c r="B99" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1">
+        <v>99.0</v>
+      </c>
+      <c r="B100" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="B101" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1">
+        <v>101.0</v>
+      </c>
+      <c r="B102" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="B103" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1">
+        <v>103.0</v>
+      </c>
+      <c r="B104" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1">
+        <v>104.0</v>
+      </c>
+      <c r="B105" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1">
+        <v>105.0</v>
+      </c>
+      <c r="B106" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1">
+        <v>106.0</v>
+      </c>
+      <c r="B107" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1">
+        <v>107.0</v>
+      </c>
+      <c r="B108" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1">
+        <v>108.0</v>
+      </c>
+      <c r="B109" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1">
+        <v>109.0</v>
+      </c>
+      <c r="B110" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1">
+        <v>110.0</v>
+      </c>
+      <c r="B111" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1">
+        <v>111.0</v>
+      </c>
+      <c r="B112" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1">
+        <v>112.0</v>
+      </c>
+      <c r="B113" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1">
+        <v>113.0</v>
+      </c>
+      <c r="B114" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1">
+        <v>114.0</v>
+      </c>
+      <c r="B115" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1">
+        <v>115.0</v>
+      </c>
+      <c r="B116" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1">
+        <v>116.0</v>
+      </c>
+      <c r="B117" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1">
+        <v>117.0</v>
+      </c>
+      <c r="B118" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1">
+        <v>118.0</v>
+      </c>
+      <c r="B119" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1">
+        <v>119.0</v>
+      </c>
+      <c r="B120" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1">
+        <v>120.0</v>
+      </c>
+      <c r="B121" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1">
+        <v>121.0</v>
+      </c>
+      <c r="B122" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1">
+        <v>122.0</v>
+      </c>
+      <c r="B123" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1">
+        <v>123.0</v>
+      </c>
+      <c r="B124" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1">
+        <v>124.0</v>
+      </c>
+      <c r="B125" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1">
+        <v>125.0</v>
+      </c>
+      <c r="B126" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1">
+        <v>126.0</v>
+      </c>
+      <c r="B127" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1">
+        <v>127.0</v>
+      </c>
+      <c r="B128" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1">
+        <v>128.0</v>
+      </c>
+      <c r="B129" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1">
+        <v>129.0</v>
+      </c>
+      <c r="B130" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1">
+        <v>130.0</v>
+      </c>
+      <c r="B131" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1">
+        <v>131.0</v>
+      </c>
+      <c r="B132" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1">
+        <v>132.0</v>
+      </c>
+      <c r="B133" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1">
+        <v>133.0</v>
+      </c>
+      <c r="B134" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1">
+        <v>134.0</v>
+      </c>
+      <c r="B135" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1">
+        <v>135.0</v>
+      </c>
+      <c r="B136" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1">
+        <v>136.0</v>
+      </c>
+      <c r="B137" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1">
+        <v>137.0</v>
+      </c>
+      <c r="B138" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1">
+        <v>138.0</v>
+      </c>
+      <c r="B139" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1">
+        <v>139.0</v>
+      </c>
+      <c r="B140" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1">
+        <v>140.0</v>
+      </c>
+      <c r="B141" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1">
+        <v>141.0</v>
+      </c>
+      <c r="B142" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1">
+        <v>142.0</v>
+      </c>
+      <c r="B143" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1">
+        <v>143.0</v>
+      </c>
+      <c r="B144" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1">
+        <v>144.0</v>
+      </c>
+      <c r="B145" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1">
+        <v>145.0</v>
+      </c>
+      <c r="B146" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1">
+        <v>146.0</v>
+      </c>
+      <c r="B147" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1">
+        <v>147.0</v>
+      </c>
+      <c r="B148" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1">
+        <v>148.0</v>
+      </c>
+      <c r="B149" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>149.0</v>
+      </c>
+      <c r="B150" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="B151" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>151.0</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>152.0</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>153.0</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>154.0</v>
+      </c>
+      <c r="B155" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>155.0</v>
+      </c>
+      <c r="B156" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>156.0</v>
+      </c>
+      <c r="B157" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1">
+        <v>157.0</v>
+      </c>
+      <c r="B158" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1">
+        <v>158.0</v>
+      </c>
+      <c r="B159" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1">
+        <v>159.0</v>
+      </c>
+      <c r="B160" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1">
+        <v>160.0</v>
+      </c>
+      <c r="B161" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1">
+        <v>161.0</v>
+      </c>
+      <c r="B162" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1">
+        <v>162.0</v>
+      </c>
+      <c r="B163" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1">
+        <v>163.0</v>
+      </c>
+      <c r="B164" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1">
+        <v>164.0</v>
+      </c>
+      <c r="B165" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1">
+        <v>165.0</v>
+      </c>
+      <c r="B166" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1">
+        <v>166.0</v>
+      </c>
+      <c r="B167" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1">
+        <v>167.0</v>
+      </c>
+      <c r="B168" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1">
+        <v>168.0</v>
+      </c>
+      <c r="B169" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1">
+        <v>169.0</v>
+      </c>
+      <c r="B170" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1">
+        <v>170.0</v>
+      </c>
+      <c r="B171" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1">
+        <v>171.0</v>
+      </c>
+      <c r="B172" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1">
+        <v>172.0</v>
+      </c>
+      <c r="B173" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1">
+        <v>173.0</v>
+      </c>
+      <c r="B174" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1">
+        <v>174.0</v>
+      </c>
+      <c r="B175" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1">
+        <v>175.0</v>
+      </c>
+      <c r="B176" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1">
+        <v>176.0</v>
+      </c>
+      <c r="B177" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1">
+        <v>177.0</v>
+      </c>
+      <c r="B178" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1">
+        <v>178.0</v>
+      </c>
+      <c r="B179" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1">
+        <v>179.0</v>
+      </c>
+      <c r="B180" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="B181" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1">
+        <v>181.0</v>
+      </c>
+      <c r="B182" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1">
+        <v>182.0</v>
+      </c>
+      <c r="B183" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1">
+        <v>183.0</v>
+      </c>
+      <c r="B184" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1">
+        <v>184.0</v>
+      </c>
+      <c r="B185" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1">
+        <v>185.0</v>
+      </c>
+      <c r="B186" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1">
+        <v>186.0</v>
+      </c>
+      <c r="B187" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1">
+        <v>187.0</v>
+      </c>
+      <c r="B188" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1">
+        <v>188.0</v>
+      </c>
+      <c r="B189" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1">
+        <v>189.0</v>
+      </c>
+      <c r="B190" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1">
+        <v>190.0</v>
+      </c>
+      <c r="B191" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1">
+        <v>191.0</v>
+      </c>
+      <c r="B192" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1">
+        <v>192.0</v>
+      </c>
+      <c r="B193" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1">
+        <v>193.0</v>
+      </c>
+      <c r="B194" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1">
+        <v>194.0</v>
+      </c>
+      <c r="B195" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1">
+        <v>195.0</v>
+      </c>
+      <c r="B196" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1">
+        <v>196.0</v>
+      </c>
+      <c r="B197" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1">
+        <v>197.0</v>
+      </c>
+      <c r="B198" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1">
+        <v>198.0</v>
+      </c>
+      <c r="B199" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1">
+        <v>199.0</v>
+      </c>
+      <c r="B200" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1">
+        <v>200.0</v>
+      </c>
+      <c r="B201" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1">
+        <v>201.0</v>
+      </c>
+      <c r="B202" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1">
+        <v>202.0</v>
+      </c>
+      <c r="B203" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1">
+        <v>203.0</v>
+      </c>
+      <c r="B204" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1">
+        <v>204.0</v>
+      </c>
+      <c r="B205" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1">
+        <v>205.0</v>
+      </c>
+      <c r="B206" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1">
+        <v>206.0</v>
+      </c>
+      <c r="B207" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1">
+        <v>207.0</v>
+      </c>
+      <c r="B208" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1">
+        <v>208.0</v>
+      </c>
+      <c r="B209" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1">
+        <v>209.0</v>
+      </c>
+      <c r="B210" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1">
+        <v>210.0</v>
+      </c>
+      <c r="B211" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1">
+        <v>211.0</v>
+      </c>
+      <c r="B212" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1">
+        <v>212.0</v>
+      </c>
+      <c r="B213" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1">
+        <v>213.0</v>
+      </c>
+      <c r="B214" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1">
+        <v>214.0</v>
+      </c>
+      <c r="B215" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1">
+        <v>215.0</v>
+      </c>
+      <c r="B216" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1">
+        <v>216.0</v>
+      </c>
+      <c r="B217" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1">
+        <v>217.0</v>
+      </c>
+      <c r="B218" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1">
+        <v>218.0</v>
+      </c>
+      <c r="B219" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1">
+        <v>219.0</v>
+      </c>
+      <c r="B220" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1">
+        <v>220.0</v>
+      </c>
+      <c r="B221" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1">
+        <v>221.0</v>
+      </c>
+      <c r="B222" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1">
+        <v>222.0</v>
+      </c>
+      <c r="B223" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1">
+        <v>223.0</v>
+      </c>
+      <c r="B224" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1">
+        <v>224.0</v>
+      </c>
+      <c r="B225" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1">
+        <v>225.0</v>
+      </c>
+      <c r="B226" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1">
+        <v>226.0</v>
+      </c>
+      <c r="B227" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1">
+        <v>227.0</v>
+      </c>
+      <c r="B228" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1">
+        <v>228.0</v>
+      </c>
+      <c r="B229" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1">
+        <v>229.0</v>
+      </c>
+      <c r="B230" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1">
+        <v>230.0</v>
+      </c>
+      <c r="B231" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1">
+        <v>231.0</v>
+      </c>
+      <c r="B232" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1">
+        <v>232.0</v>
+      </c>
+      <c r="B233" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1">
+        <v>233.0</v>
+      </c>
+      <c r="B234" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1">
+        <v>234.0</v>
+      </c>
+      <c r="B235" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1">
+        <v>235.0</v>
+      </c>
+      <c r="B236" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1">
+        <v>236.0</v>
+      </c>
+      <c r="B237" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1">
+        <v>237.0</v>
+      </c>
+      <c r="B238" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1">
+        <v>238.0</v>
+      </c>
+      <c r="B239" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1">
+        <v>239.0</v>
+      </c>
+      <c r="B240" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1">
+        <v>240.0</v>
+      </c>
+      <c r="B241" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1">
+        <v>241.0</v>
+      </c>
+      <c r="B242" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1">
+        <v>242.0</v>
+      </c>
+      <c r="B243" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1">
+        <v>243.0</v>
+      </c>
+      <c r="B244" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1">
+        <v>244.0</v>
+      </c>
+      <c r="B245" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1">
+        <v>245.0</v>
+      </c>
+      <c r="B246" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1">
+        <v>246.0</v>
+      </c>
+      <c r="B247" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1">
+        <v>247.0</v>
+      </c>
+      <c r="B248" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1">
+        <v>248.0</v>
+      </c>
+      <c r="B249" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1">
+        <v>249.0</v>
+      </c>
+      <c r="B250" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1">
+        <v>250.0</v>
+      </c>
+      <c r="B251" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1">
+        <v>251.0</v>
+      </c>
+      <c r="B252" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1">
+        <v>252.0</v>
+      </c>
+      <c r="B253" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1">
+        <v>253.0</v>
+      </c>
+      <c r="B254" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1">
+        <v>254.0</v>
+      </c>
+      <c r="B255" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1">
+        <v>255.0</v>
+      </c>
+      <c r="B256" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1">
+        <v>256.0</v>
+      </c>
+      <c r="B257" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1">
+        <v>257.0</v>
+      </c>
+      <c r="B258" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1">
+        <v>258.0</v>
+      </c>
+      <c r="B259" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1">
+        <v>259.0</v>
+      </c>
+      <c r="B260" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1">
+        <v>260.0</v>
+      </c>
+      <c r="B261" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1">
+        <v>261.0</v>
+      </c>
+      <c r="B262" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1">
+        <v>262.0</v>
+      </c>
+      <c r="B263" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1">
+        <v>263.0</v>
+      </c>
+      <c r="B264" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1">
+        <v>264.0</v>
+      </c>
+      <c r="B265" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1">
+        <v>265.0</v>
+      </c>
+      <c r="B266" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1">
+        <v>266.0</v>
+      </c>
+      <c r="B267" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1">
+        <v>267.0</v>
+      </c>
+      <c r="B268" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1">
+        <v>268.0</v>
+      </c>
+      <c r="B269" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1">
+        <v>269.0</v>
+      </c>
+      <c r="B270" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1">
+        <v>270.0</v>
+      </c>
+      <c r="B271" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1">
+        <v>271.0</v>
+      </c>
+      <c r="B272" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1">
+        <v>272.0</v>
+      </c>
+      <c r="B273" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1">
+        <v>273.0</v>
+      </c>
+      <c r="B274" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1">
+        <v>274.0</v>
+      </c>
+      <c r="B275" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1">
+        <v>275.0</v>
+      </c>
+      <c r="B276" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1">
+        <v>276.0</v>
+      </c>
+      <c r="B277" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1">
+        <v>277.0</v>
+      </c>
+      <c r="B278" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1">
+        <v>278.0</v>
+      </c>
+      <c r="B279" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1">
+        <v>279.0</v>
+      </c>
+      <c r="B280" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1">
+        <v>280.0</v>
+      </c>
+      <c r="B281" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1">
+        <v>281.0</v>
+      </c>
+      <c r="B282" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1">
+        <v>282.0</v>
+      </c>
+      <c r="B283" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1">
+        <v>283.0</v>
+      </c>
+      <c r="B284" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1">
+        <v>284.0</v>
+      </c>
+      <c r="B285" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1">
+        <v>285.0</v>
+      </c>
+      <c r="B286" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1">
+        <v>286.0</v>
+      </c>
+      <c r="B287" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1">
+        <v>287.0</v>
+      </c>
+      <c r="B288" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1">
+        <v>288.0</v>
+      </c>
+      <c r="B289" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1">
+        <v>289.0</v>
+      </c>
+      <c r="B290" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1">
+        <v>290.0</v>
+      </c>
+      <c r="B291" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1">
+        <v>291.0</v>
+      </c>
+      <c r="B292" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1">
+        <v>292.0</v>
+      </c>
+      <c r="B293" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1">
+        <v>293.0</v>
+      </c>
+      <c r="B294" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1">
+        <v>294.0</v>
+      </c>
+      <c r="B295" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1">
+        <v>295.0</v>
+      </c>
+      <c r="B296" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1">
+        <v>296.0</v>
+      </c>
+      <c r="B297" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1">
+        <v>297.0</v>
+      </c>
+      <c r="B298" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1">
+        <v>298.0</v>
+      </c>
+      <c r="B299" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1">
+        <v>299.0</v>
+      </c>
+      <c r="B300" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="B301" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1">
+        <v>301.0</v>
+      </c>
+      <c r="B302" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1">
+        <v>302.0</v>
+      </c>
+      <c r="B303" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1">
+        <v>303.0</v>
+      </c>
+      <c r="B304" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1">
+        <v>304.0</v>
+      </c>
+      <c r="B305" s="1">
+        <v>97.0</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1">
+        <v>305.0</v>
+      </c>
+      <c r="B306" s="1">
+        <v>97.0</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1">
+        <v>306.0</v>
+      </c>
+      <c r="B307" s="1">
+        <v>97.0</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1">
+        <v>307.0</v>
+      </c>
+      <c r="B308" s="1">
+        <v>98.0</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1">
+        <v>308.0</v>
+      </c>
+      <c r="B309" s="1">
+        <v>98.0</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1">
+        <v>309.0</v>
+      </c>
+      <c r="B310" s="1">
+        <v>98.0</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1">
+        <v>310.0</v>
+      </c>
+      <c r="B311" s="1">
+        <v>99.0</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1">
+        <v>311.0</v>
+      </c>
+      <c r="B312" s="1">
+        <v>99.0</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1">
+        <v>312.0</v>
+      </c>
+      <c r="B313" s="1">
+        <v>99.0</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1">
+        <v>313.0</v>
+      </c>
+      <c r="B314" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1">
+        <v>314.0</v>
+      </c>
+      <c r="B315" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1">
+        <v>315.0</v>
+      </c>
+      <c r="B316" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1">
+        <v>316.0</v>
+      </c>
+      <c r="B317" s="1">
+        <v>101.0</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1">
+        <v>317.0</v>
+      </c>
+      <c r="B318" s="1">
+        <v>101.0</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1">
+        <v>318.0</v>
+      </c>
+      <c r="B319" s="1">
+        <v>101.0</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1">
+        <v>319.0</v>
+      </c>
+      <c r="B320" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1">
+        <v>320.0</v>
+      </c>
+      <c r="B321" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1">
+        <v>321.0</v>
+      </c>
+      <c r="B322" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1">
+        <v>322.0</v>
+      </c>
+      <c r="B323" s="1">
+        <v>103.0</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1">
+        <v>323.0</v>
+      </c>
+      <c r="B324" s="1">
+        <v>103.0</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1">
+        <v>324.0</v>
+      </c>
+      <c r="B325" s="1">
+        <v>103.0</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1">
+        <v>325.0</v>
+      </c>
+      <c r="B326" s="1">
+        <v>104.0</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1">
+        <v>326.0</v>
+      </c>
+      <c r="B327" s="1">
+        <v>104.0</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1">
+        <v>327.0</v>
+      </c>
+      <c r="B328" s="1">
+        <v>104.0</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1">
+        <v>328.0</v>
+      </c>
+      <c r="B329" s="1">
+        <v>105.0</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1">
+        <v>329.0</v>
+      </c>
+      <c r="B330" s="1">
+        <v>105.0</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1">
+        <v>330.0</v>
+      </c>
+      <c r="B331" s="1">
+        <v>105.0</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1">
+        <v>331.0</v>
+      </c>
+      <c r="B332" s="1">
+        <v>106.0</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1">
+        <v>332.0</v>
+      </c>
+      <c r="B333" s="1">
+        <v>106.0</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1">
+        <v>333.0</v>
+      </c>
+      <c r="B334" s="1">
+        <v>106.0</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1">
+        <v>334.0</v>
+      </c>
+      <c r="B335" s="1">
+        <v>107.0</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1">
+        <v>335.0</v>
+      </c>
+      <c r="B336" s="1">
+        <v>107.0</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1">
+        <v>336.0</v>
+      </c>
+      <c r="B337" s="1">
+        <v>107.0</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1">
+        <v>337.0</v>
+      </c>
+      <c r="B338" s="1">
+        <v>108.0</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1">
+        <v>338.0</v>
+      </c>
+      <c r="B339" s="1">
+        <v>108.0</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1">
+        <v>339.0</v>
+      </c>
+      <c r="B340" s="1">
+        <v>108.0</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1">
+        <v>340.0</v>
+      </c>
+      <c r="B341" s="1">
+        <v>109.0</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1">
+        <v>341.0</v>
+      </c>
+      <c r="B342" s="1">
+        <v>109.0</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1">
+        <v>342.0</v>
+      </c>
+      <c r="B343" s="1">
+        <v>109.0</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1">
+        <v>343.0</v>
+      </c>
+      <c r="B344" s="1">
+        <v>110.0</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1">
+        <v>344.0</v>
+      </c>
+      <c r="B345" s="1">
+        <v>110.0</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1">
+        <v>345.0</v>
+      </c>
+      <c r="B346" s="1">
+        <v>110.0</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1">
+        <v>346.0</v>
+      </c>
+      <c r="B347" s="1">
+        <v>111.0</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1">
+        <v>347.0</v>
+      </c>
+      <c r="B348" s="1">
+        <v>111.0</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1">
+        <v>348.0</v>
+      </c>
+      <c r="B349" s="1">
+        <v>111.0</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/procedure_lookup_project.xlsx
+++ b/procedure_lookup_project.xlsx
@@ -19,14 +19,15 @@
   <definedNames>
     <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">ProcedureClinics!$A$1:$F$1185</definedName>
     <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">ProcedureRadiologists!$A$1:$E$2271</definedName>
-    <definedName hidden="1" localSheetId="8" name="_xlnm._FilterDatabase">ProcedureBookingCategories!$A$1:$F$1539</definedName>
+    <definedName hidden="1" localSheetId="8" name="_xlnm._FilterDatabase">ProcedureBookingCategories!$A$1:$F$1540</definedName>
+    <definedName hidden="1" localSheetId="10" name="_xlnm._FilterDatabase">ProcedureAliases!$A$1:$D$360</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4433" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4455" uniqueCount="748">
   <si>
     <t>Table</t>
   </si>
@@ -2227,6 +2228,36 @@
     <t>Kneecap Bursa Injection</t>
   </si>
   <si>
+    <t>Any other joint aspiration</t>
+  </si>
+  <si>
+    <t>Joint Aspiration Other</t>
+  </si>
+  <si>
+    <t>Piriformis Botox</t>
+  </si>
+  <si>
+    <t>Piri Botox Injection</t>
+  </si>
+  <si>
+    <t>Botox Injection</t>
+  </si>
+  <si>
+    <t>TMJ Botox Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMJ </t>
+  </si>
+  <si>
+    <t>TMJ Migraines</t>
+  </si>
+  <si>
+    <t>Migraine Botox</t>
+  </si>
+  <si>
+    <t>Botox Head ache</t>
+  </si>
+  <si>
     <t>ProcedureRuleID</t>
   </si>
   <si>
@@ -2600,8 +2631,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F1539" displayName="tbProcedureBookingCategories" name="tbProcedureBookingCategories" id="8">
-  <autoFilter ref="$A$1:$F$1539"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F1540" displayName="tbProcedureBookingCategories" name="tbProcedureBookingCategories" id="8">
+  <autoFilter ref="$A$1:$F$1540"/>
   <tableColumns count="6">
     <tableColumn name="ProcedureBookingCategoryID" id="1"/>
     <tableColumn name="ProcedureID" id="2"/>
@@ -2615,7 +2646,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D349" displayName="tbProcedureAliases" name="tbProcedureAliases" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D360" displayName="tbProcedureAliases" name="tbProcedureAliases" id="9">
+  <autoFilter ref="$A$1:$D$360"/>
   <tableColumns count="4">
     <tableColumn name="ProcedureAliasID" id="1"/>
     <tableColumn name="ProcedureID" id="2"/>
@@ -7876,6 +7908,160 @@
         <v>489</v>
       </c>
     </row>
+    <row r="350" ht="22.5" customHeight="1">
+      <c r="A350" s="6">
+        <v>349.0</v>
+      </c>
+      <c r="B350" s="6">
+        <v>115.0</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="D350" s="6" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="351" ht="22.5" customHeight="1">
+      <c r="A351" s="6">
+        <v>350.0</v>
+      </c>
+      <c r="B351" s="6">
+        <v>115.0</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="352" ht="22.5" customHeight="1">
+      <c r="A352" s="6">
+        <v>351.0</v>
+      </c>
+      <c r="B352" s="6">
+        <v>114.0</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="353" ht="22.5" customHeight="1">
+      <c r="A353" s="6">
+        <v>352.0</v>
+      </c>
+      <c r="B353" s="6">
+        <v>114.0</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="D353" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="354" ht="22.5" customHeight="1">
+      <c r="A354" s="6">
+        <v>353.0</v>
+      </c>
+      <c r="B354" s="6">
+        <v>114.0</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="355" ht="22.5" customHeight="1">
+      <c r="A355" s="6">
+        <v>354.0</v>
+      </c>
+      <c r="B355" s="6">
+        <v>113.0</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="356" ht="22.5" customHeight="1">
+      <c r="A356" s="6">
+        <v>355.0</v>
+      </c>
+      <c r="B356" s="6">
+        <v>113.0</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="357" ht="22.5" customHeight="1">
+      <c r="A357" s="6">
+        <v>356.0</v>
+      </c>
+      <c r="B357" s="6">
+        <v>113.0</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="358" ht="22.5" customHeight="1">
+      <c r="A358" s="6">
+        <v>357.0</v>
+      </c>
+      <c r="B358" s="6">
+        <v>112.0</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="359" ht="22.5" customHeight="1">
+      <c r="A359" s="6">
+        <v>358.0</v>
+      </c>
+      <c r="B359" s="6">
+        <v>112.0</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="360" ht="22.5" customHeight="1">
+      <c r="A360" s="6">
+        <v>359.0</v>
+      </c>
+      <c r="B360" s="6">
+        <v>112.0</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>708</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A1000">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -7909,22 +8095,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>281</v>
@@ -90908,6 +91094,24 @@
       </c>
       <c r="F1539" s="7"/>
     </row>
+    <row r="1540" ht="22.5" customHeight="1">
+      <c r="A1540" s="6">
+        <v>1635.0</v>
+      </c>
+      <c r="B1540" s="6">
+        <v>46.0</v>
+      </c>
+      <c r="C1540" s="6">
+        <v>33.0</v>
+      </c>
+      <c r="D1540" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E1540" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F1540" s="7"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A1811 C1527:C1538">
     <cfRule type="expression" dxfId="5" priority="1">
